--- a/submission/knowledge/A06-武汉交通住宿管家/武汉交通住宿管家QA导入表.xlsx
+++ b/submission/knowledge/A06-武汉交通住宿管家/武汉交通住宿管家QA导入表.xlsx
@@ -367,6 +367,601 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁怎么扫码？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metro新时代、支付宝、微信、云闪付等可开通乘车码。进出同一APP。也可售票机买单程票。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">扫码</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要办武汉通吗？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">短途游客不必。车站可充值代售。挂失去指定网点。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉通</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外地老人地铁免费吗？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本地老年卡规则不能直接套外地游客。看武汉地铁当天规定。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">免费</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去省博坐哪？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公开提示地铁8号线省博湖北日报站等，以导视为准。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">几号线</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼能停车吗？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">紧张，建议地铁。收费看现场。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">停车</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深夜落地？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可能无地铁，准备出租。不编班次。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场大巴几点？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以机场交通中心当天为准。我不背时刻表。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大巴</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有没有免费直达黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要默认存在这种专线。地铁2号线进城再换乘。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">专线</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜游散场还有地铁吗？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对照结束时间和站内广播，不保证。准备出租。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">末班</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半夜坐轮渡？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武中线公开时段到晚上约20:00，夜间不当回家方式。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轮渡夜</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁晚了误机？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">预留安检时间。故障听广播。我不承担航班责任。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">误机</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2号线在机场叫什么站？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天河机场站。仍以站内导视为准。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">行李多坐大巴还是地铁？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大件少换乘更稳。大巴时刻以机场交通中心当天为准，我不背表。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">票面写汉口站却去了武汉站？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先确认三座站不是同一个。改乘地铁或出租，耗时因拥堵而异。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车站</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武昌站出站去黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">相对近老城，仍有步行。出入口以导视为准。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车站</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进出必须同一APP吗？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乘车码须同一客户端进出、一人一码。也可售票机买单程票。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉通在哪充？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车站客服中心可代售充值。挂失去指定网点。短途游客不必办。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节假日会延时吗？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">市政府报道有过2、4号线延时先例。仍以当天公告和广播为准。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去古琴台几号线？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6号线琴台站，再步行。车位少。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去汉街呢？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出站名以地铁APP和现场为准，我不背可能改名的出入口编号。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武中线多少钱？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省文旅厅2026年5月转载约1.5元。以轮渡公司当天为准。咨询转载027-82833509。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轮渡</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能带自行车吗？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以轮渡公司当日规定为准，不要默认可以。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轮渡</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼门口能不能停？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按交管点上下客，不要让司机违停在门口。车位紧张建议地铁。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出租</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过江网约车一口价？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不报死价。拥堵差异大。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出租</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住汉阳图什么？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近古琴台、晴川、龟山。餐饮夜班密度可能不如汉口，要接受。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住汉口图什么？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路、江滩、夜生活方便。早上看黄鹤楼要过江。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住武昌图什么？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">早上看楼、户部巷少过江。去汉口夜景要预留回程。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">景区门口日租靠谱吗？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只推荐有证酒店。不报房价、不订房。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁能进推车吗？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问车站工作人员闸机和电梯。现场为准。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外地老人有老年卡吗？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本地老年卡规则不能直接套外地游客。看武汉地铁当天规定。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">散场回汉口还有轮渡吗？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武中线公开时段到晚上约20:00，夜间不当回家方式。改地铁或出租。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜游</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁停运怎么走？</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听广播。改其他线路、公交或出租。人群别推挤，受伤120。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">故障</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我买高铁票。</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。我只管进城接驳原则。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼几点开门？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问景点讲解员。我不管开园表。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">酒店含早算过早吗？</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本地过早是街头面馆那一套。酒店自助是另一回事，吃什么问美食顾问。</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>